--- a/pensum/ol15/OL15_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol15/OL15_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="170">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 15: Nyere organisasjonsteorier (V5)</t>
   </si>
@@ -146,9 +146,18 @@
     <t xml:space="preserve">a)  Hvor mange prosent falt tiden per serviceoppdrag den første måneden? (Før − etter) delt på før, i prosent med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endring i prosent = (før − etter) / før × 100. Hawthorne-effekten: de som deltar i et forsøk, har en tendens til å forsterke den atferden de tror forventes (Organisasjon og ledelse 15.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mange kroner i året er gevinsten verdt hvis nedgangen varer, og de frigjorte timene selges til andre kunder? Oppdrag × spart tid × timepris.</t>
   </si>
   <si>
+    <t xml:space="preserve">Gevinst = antall oppdrag × spart tid × timepris. Forbeholdet bygger på Hawthorne-effekten (Organisasjon og ledelse 15.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hva er den mest sannsynlige forklaringen på nedgangen etter bare én måned, hvis vi bruker funnene fra Hawthorne-undersøkelsene?   A: Systemet gjør selve arbeidet raskere   B: Montørene vet at noen følger med: Hawthorne-effekten   C: Gruppenormene i avdelingen har brutt sammen   (skriv bokstaven)</t>
   </si>
   <si>
@@ -173,6 +182,24 @@
     <t xml:space="preserve">e)  Tom sier: «Det viser at de må overvåkes. Nå ser vi hvem som har latet seg.» Hvilket menneskesyn uttrykker han, hva kan det gjøre med montørene ifølge McGregor og Argyris, og hva bør Kari gjøre med systemet og tallet? Tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Teori X og teori Y (McGregor, Organisasjon og ledelse 15.3), pyramidale verdier og vi-mot-dem-holdning (Argyris, 15.2), Hawthorne-effekten (15.1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nedgang i prosent: (6 − 5) / 6 × 100. Gevinsten i året: 210 oppdrag × 1 spart time × 890 kr. Spør deg så: hva er det tallet bygger på?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hawthorne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hva var det eneste nye den første måneden? Forskerne fant at produktiviteten steg også i kontrollgruppen, der ingenting ble endret. Hva fikk arbeiderne der?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 15, avsnitt 15.1 (Hawthorne-undersøkelsene, Hawthorne-effekten) og 15.3 (teori X og teori Y). Timepris og serviceoppdrag: faktaarket. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -266,12 +293,30 @@
     <t xml:space="preserve">c)  Hvor mange kroner i fakturerbar tid koster det å undersøke de 4 ukjente fabrikatene grundig, 2 timer hver, når timene ellers ville vært fakturert til 890 kr?</t>
   </si>
   <si>
+    <t xml:space="preserve">Kostnad = antall alternativer × timer per alternativ × timepris. Mangel på tid og ressurser er en av Simons begrensninger (Organisasjon og ledelse 15.4).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  En student sier: «Begrenset rasjonalitet betyr at Mona ikke trenger å vurdere alternativer.» Hva er riktig?   A: Studenten har rett: Simon fritar lederen fra å undersøke   B: Valget er irrasjonelt og bør gjøres om   C: Ingen beslutning er fullt rasjonell; lederen søker et tilfredsstillende resultat innenfor begrensningene   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Den ene montøren vil planlegge uka selv og snakke med kundene; den andre vil helst få arbeidsordren og jobbe i fred. Hvordan bør Mona lede de to? Bruk McGregor og Argyris. Tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Teori Y (McGregor, Organisasjon og ledelse 15.3), selvrealisering og stillingsutvidelse (Argyris, 15.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Det økonomiske mennesket maksimerer. Det administrative mennesket søker et tilfredsstillende resultat innenfor begrensningene. Begrensningene er kunnskap om problemet, alternativene og konsekvensene, og tid og ressurser.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regningen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 ukjente fabrikater × 2 timer × 890 kr. For e: les teori Y hos McGregor, og Argyris' eget forbehold om at ikke alle er opptatt av selvrealisering.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 15, avsnitt 15.4 (Simon: begrenset rasjonalitet, det administrative mennesket), 15.2 (Argyris) og 15.3 (McGregor). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -329,9 +374,15 @@
     <t xml:space="preserve">a)  Hvor mange prosent av Nordlys' 14 400 fakturerbare timer i året binder prosjektet? Én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Andel = del / helhet × 100. Et prosjekt skal løses innenfor en bestemt tids- og kostnadsramme (Organisasjon og ledelse 15.8.5).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mange prosent av de 14 utførende trenger prosjektet? Én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Andel = del / helhet × 100. Prosjektoppgaven krever ofte tverrfaglig innsats (Organisasjon og ledelse 15.8.5).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Ja eller nei: kjennetegner dette rehabiliteringen som en prosjektoppgave slik boka beskriver den (15.8.5)?</t>
   </si>
   <si>
@@ -359,6 +410,21 @@
     <t xml:space="preserve">e)  Styret spør hvordan prosjektet bør organiseres, og hva som er den største risikoen. Gi en anbefaling med minst ett tall. Tre–fire setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Prosjektorganisasjon med kontrollerende eller full autoritet, og matrise (Organisasjon og ledelse 15.8.5, figur 15.7–15.9). Enhetlig ledelse (14.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andelene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapasiteten: 2 400 delt på 14 400. Folkene: 2 + 4 + 2 delt på 14. Svar i prosent med én desimal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boka gir seks kjennetegn på en prosjektoppgave (15.8.5). Faste regler er maskinbyråkratiet. Når folk har både en fast sjef og en prosjektleder, går autoriteten to veier.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 15, avsnitt 15.8.5 (den innovative organisasjonen, prosjektoppgavens kjennetegn, matrise, prosjektorganisasjon med kontrollerende og full autoritet) og kap. 14.2 (enhetlig ledelse). Tallene er fra appens eksamensoppgave og faktaarket. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -443,10 +509,28 @@
     <t xml:space="preserve">c)  Hvor mange prosent av Fjells 3 500 fakturerbare timer står Mona selv for?</t>
   </si>
   <si>
+    <t xml:space="preserve">Andel = del / helhet × 100. I entreprenørorganisasjonen er toppledelsen også en del av den operative kjernen (Organisasjon og ledelse 15.8.1 og 15.7).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Hva sier Mintzbergs situasjonsteori om formalisering hos Fjell?   A: Fjell bør skrive stillingsinstrukser og regler for alt nå, fordi formalisering alltid er riktig   B: Fjell bør aldri formalisere, fordi entreprenørorganisasjonen er fleksibel   C: Behovet for formalisering øker med størrelsen; det er lite nå, men vokser når Fjell ansetter flere   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Mona skal ansette en tredje montør og en lærling. Bruk to av Mintzbergs situasjonsvariabler og si hva hun bør formalisere først, og hva hun kan la være. Tre setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mintzbergs situasjonsvariabler: alder, størrelse, produksjonsprosess, maktforhold og omgivelser (Organisasjon og ledelse 15.6.1–15.6.5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typen og delene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hvor mange av Mintzbergs fem deler har Fjell? Den operative kjernen er der inntektene skapes, og boka legger markedsføring og salg dit. Planlegging og økonomistyring er teknostrukturens oppgave.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formalisering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monas andel: 700 / 3 500. Mintzberg: behovet for formalisering øker med størrelsen. Hva endrer seg når tre blir fem, og hvem er knapp i arbeidsmarkedet?</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 15, avsnitt 15.6 (situasjonsvariablene, særlig størrelse og maktforhold), 15.7 (organisasjonens fem hoveddeler) og 15.8.1 (entreprenørorganisasjonen). Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -460,7 +544,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,8 +611,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -544,13 +650,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -603,7 +727,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -680,11 +804,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -721,8 +865,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -736,7 +880,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -750,7 +894,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1053,7 +1197,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1203,33 +1347,18 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="18" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(186900))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="B18" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="18" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
@@ -1239,154 +1368,251 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="F20" s="16"/>
+      <c r="G20" s="18" t="str">
+        <f aca="false">IF(F20="","",IF(ABS(F20-(186900))&lt;=1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="18" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="18" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="19"/>
+      <c r="F23" s="21"/>
       <c r="G23" s="18" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="18" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="19"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="18" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-    </row>
-    <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+      <c r="F26" s="21"/>
+      <c r="G26" s="18" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="18" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="18" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="18" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+    </row>
+    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="23">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1403,7 +1629,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1414,7 +1640,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1424,7 +1650,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1435,7 +1661,7 @@
     </row>
     <row r="5" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1446,10 +1672,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -1458,11 +1684,11 @@
       <c r="G7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>56</v>
+      <c r="A8" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1471,11 +1697,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>58</v>
+      <c r="A9" s="26" t="s">
+        <v>67</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1484,11 +1710,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>60</v>
+      <c r="A10" s="26" t="s">
+        <v>69</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1497,11 +1723,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>62</v>
+      <c r="A11" s="26" t="s">
+        <v>71</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1510,11 +1736,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>64</v>
+      <c r="A12" s="26" t="s">
+        <v>73</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1523,11 +1749,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>66</v>
+      <c r="A13" s="26" t="s">
+        <v>75</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1536,11 +1762,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>68</v>
+      <c r="A14" s="26" t="s">
+        <v>77</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1549,11 +1775,11 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
-        <v>70</v>
+      <c r="A15" s="26" t="s">
+        <v>79</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1578,13 +1804,13 @@
     </row>
     <row r="18" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="19"/>
+      <c r="F18" s="21"/>
       <c r="G18" s="18" t="str">
         <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1592,7 +1818,7 @@
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1601,13 +1827,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="19"/>
+      <c r="F20" s="21"/>
       <c r="G20" s="18" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1615,13 +1841,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="19"/>
+      <c r="F21" s="21"/>
       <c r="G21" s="18" t="str">
         <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1629,13 +1855,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="19"/>
+      <c r="F22" s="21"/>
       <c r="G22" s="18" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1643,13 +1869,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="19"/>
+      <c r="F23" s="21"/>
       <c r="G23" s="18" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1657,13 +1883,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="19"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="18" t="str">
         <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1671,7 +1897,7 @@
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1683,80 +1909,143 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="18" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="C","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+    </row>
+    <row r="28" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="18" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="C","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="32" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+    </row>
+    <row r="40" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="30">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1777,11 +2066,16 @@
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1798,7 +2092,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1809,7 +2103,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1819,7 +2113,7 @@
     </row>
     <row r="4" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1830,7 +2124,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1841,10 +2135,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -1853,11 +2147,11 @@
       <c r="G7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>86</v>
+      <c r="A8" s="26" t="s">
+        <v>101</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1866,11 +2160,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>88</v>
+      <c r="A9" s="26" t="s">
+        <v>103</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1879,11 +2173,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>90</v>
+      <c r="A10" s="26" t="s">
+        <v>105</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1892,11 +2186,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>92</v>
+      <c r="A11" s="26" t="s">
+        <v>107</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1905,11 +2199,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>94</v>
+      <c r="A12" s="26" t="s">
+        <v>109</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1918,11 +2212,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>96</v>
+      <c r="A13" s="26" t="s">
+        <v>111</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1931,11 +2225,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>98</v>
+      <c r="A14" s="26" t="s">
+        <v>113</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1960,7 +2254,7 @@
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1972,187 +2266,263 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="18" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(57.1))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="19"/>
+      <c r="F20" s="16"/>
       <c r="G20" s="18" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="18" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="18" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F20="","",IF(ABS(F20-(57.1))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="18" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="19"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="18" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="19"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="18" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="19"/>
+      <c r="F26" s="21"/>
       <c r="G26" s="18" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="32" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="18" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="18" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="18" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="18" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+    </row>
+    <row r="42" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="31">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2165,19 +2535,25 @@
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A43:G43"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2194,7 +2570,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2205,7 +2581,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2215,7 +2591,7 @@
     </row>
     <row r="4" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2226,7 +2602,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2237,10 +2613,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -2249,11 +2625,11 @@
       <c r="G7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>115</v>
+      <c r="A8" s="26" t="s">
+        <v>137</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2262,11 +2638,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>117</v>
+      <c r="A9" s="26" t="s">
+        <v>139</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2275,11 +2651,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>119</v>
+      <c r="A10" s="26" t="s">
+        <v>141</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2288,11 +2664,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>121</v>
+      <c r="A11" s="26" t="s">
+        <v>143</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2301,11 +2677,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>123</v>
+      <c r="A12" s="26" t="s">
+        <v>145</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2314,11 +2690,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>125</v>
+      <c r="A13" s="26" t="s">
+        <v>147</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2327,11 +2703,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>127</v>
+      <c r="A14" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2340,11 +2716,11 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
-        <v>129</v>
+      <c r="A15" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -2369,13 +2745,13 @@
     </row>
     <row r="18" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="19"/>
+      <c r="F18" s="21"/>
       <c r="G18" s="18" t="str">
         <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2383,7 +2759,7 @@
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2392,13 +2768,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="19"/>
+      <c r="F20" s="21"/>
       <c r="G20" s="18" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2406,13 +2782,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="19"/>
+      <c r="F21" s="21"/>
       <c r="G21" s="18" t="str">
         <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2420,13 +2796,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="19"/>
+      <c r="F22" s="21"/>
       <c r="G22" s="18" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2434,13 +2810,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="19"/>
+      <c r="F23" s="21"/>
       <c r="G23" s="18" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2448,13 +2824,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="19"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="18" t="str">
         <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2462,7 +2838,7 @@
     </row>
     <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2474,80 +2850,143 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="18" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="C","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+    </row>
+    <row r="28" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="18" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="C","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="32" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+    </row>
+    <row r="40" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="30">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2568,11 +3007,16 @@
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ol15/OL15_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol15/OL15_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Hawthorne-undersøkelsene (15.1) skulle måle virkningen av det fysiske arbeidsmiljøet, men produktiviteten økte uansett hva forskerne endret, også i kontrollgruppen. Arbeiderne svarte at de gjorde sitt beste fordi de ble viet oppmerksomhet. Hawthorne-effekten: de som deltar i et forsøk, forsterker den atferden de tror forventes. McGregor (15.3) viste at de ansattes atferd langt på vei er et resultat av ledelsens menneskesyn: teori X (folk må kontrolleres og tvinges) eller teori Y (folk søker ansvar og styrer seg selv når de deler målene).</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Serviceavdelingen i Nordlys har 210 oppdrag i året, og et oppdrag har tatt 6 montørtimer. Kari innfører timeregistrering på mobil, og montørene vet at tidsbruken nå følges for hvert oppdrag. Første måned faller tiden per oppdrag til 5 timer. Kari vil utvide systemet til prosjekt og legge gevinsten inn i neste års budsjett. Timeprisen er 890 kr uten mva. Tom sier: «Det viser at de må overvåkes. Nå ser vi hvem som har latet seg.» Gå fram slik: regn nedgangen i prosent, regn hva gevinsten er verdt i året hvis den varer og timene selges, og vurder så med Hawthorne og McGregor hva tallet egentlig sier.</t>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Serviceavdelingen i Nordlys har 210 oppdrag i året, og et oppdrag har tatt 6 montørtimer. Kari innfører timeregistrering på mobil, og montørene vet at tidsbruken nå følges for hvert oppdrag. Første måned faller tiden per oppdrag til 5 timer. Kari vil utvide systemet til prosjekt og legge gevinsten inn i neste års budsjett. Timeprisen er 890 kr uten merverdiavgift. Tom sier: «Det viser at de må overvåkes. Nå ser vi hvem som har latet seg.» Gå fram slik: regn nedgangen i prosent, regn hva gevinsten er verdt i året hvis den varer og timene selges, og vurder så med Hawthorne og McGregor hva tallet egentlig sier.</t>
   </si>
   <si>
     <t xml:space="preserve">Post</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">Montørtimer per oppdrag</t>
   </si>
   <si>
-    <t xml:space="preserve">Timepris, kr uten mva</t>
+    <t xml:space="preserve">Timepris, kr uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Tidsbruken følges per oppdrag</t>

--- a/pensum/ol15/OL15_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol15/OL15_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="170">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 15: Nyere organisasjonsteorier (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 15: Nyere organisasjonsteorier (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>
